--- a/data/trans_dic/P19C05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,32</t>
+          <t>1,78; 5,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,89</t>
+          <t>1,69; 5,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,42</t>
+          <t>2,18; 6,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,94</t>
+          <t>0,09; 5,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,13</t>
+          <t>0,97; 3,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,46</t>
+          <t>2,4; 6,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,2</t>
+          <t>0,11; 4,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,94</t>
+          <t>1,69; 3,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,93</t>
+          <t>2,29; 4,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,96</t>
+          <t>2,2; 5,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,76</t>
+          <t>0,37; 3,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,25</t>
+          <t>1,98; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,19</t>
+          <t>2,25; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,57</t>
+          <t>2,77; 6,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,92</t>
+          <t>2,35; 8,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,73</t>
+          <t>2,52; 5,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,26</t>
+          <t>4,43; 8,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,31</t>
+          <t>2,14; 5,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,97</t>
+          <t>1,82; 6,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,9</t>
+          <t>2,54; 4,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,12</t>
+          <t>3,65; 6,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,34</t>
+          <t>2,81; 5,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,79</t>
+          <t>2,53; 5,72</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,0</t>
+          <t>4,82; 9,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,46</t>
+          <t>5,76; 10,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,25</t>
+          <t>2,59; 6,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,97</t>
+          <t>2,52; 6,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,92</t>
+          <t>6,43; 10,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,72</t>
+          <t>5,39; 9,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,22</t>
+          <t>4,91; 9,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,07</t>
+          <t>3,28; 6,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,32</t>
+          <t>6,18; 9,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,38</t>
+          <t>6,03; 9,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,84</t>
+          <t>4,1; 6,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,53</t>
+          <t>3,2; 5,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 16,72</t>
+          <t>9,64; 16,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 17,85</t>
+          <t>10,95; 17,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,75</t>
+          <t>7,5; 12,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,88</t>
+          <t>2,3; 8,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 16,16</t>
+          <t>9,91; 15,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 18,83</t>
+          <t>12,44; 18,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 12,36</t>
+          <t>7,23; 12,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,26</t>
+          <t>5,22; 8,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 15,15</t>
+          <t>10,55; 15,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 17,3</t>
+          <t>12,6; 17,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,54</t>
+          <t>7,98; 11,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,78</t>
+          <t>3,47; 7,94</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,14; 31,58</t>
+          <t>21,35; 31,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,94; 31,05</t>
+          <t>21,75; 30,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 21,44</t>
+          <t>13,12; 21,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,06</t>
+          <t>9,27; 14,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 29,79</t>
+          <t>19,34; 29,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 28,68</t>
+          <t>19,72; 29,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,2; 21,0</t>
+          <t>13,45; 21,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 11,7</t>
+          <t>7,61; 11,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,85; 28,49</t>
+          <t>21,67; 28,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,86; 28,75</t>
+          <t>22,01; 28,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,69; 20,68</t>
+          <t>14,56; 20,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 12,06</t>
+          <t>9,08; 11,97</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,6; 45,8</t>
+          <t>32,44; 45,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,54; 47,15</t>
+          <t>34,21; 47,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,42; 31,41</t>
+          <t>19,31; 31,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,22; 21,99</t>
+          <t>15,63; 22,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,75; 47,85</t>
+          <t>36,0; 47,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,3; 48,77</t>
+          <t>36,61; 48,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,48; 33,46</t>
+          <t>22,28; 33,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 23,96</t>
+          <t>6,39; 24,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,21; 44,68</t>
+          <t>35,96; 44,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,93; 45,69</t>
+          <t>37,2; 46,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,58; 31,03</t>
+          <t>22,85; 31,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,33; 21,64</t>
+          <t>8,34; 21,62</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,88; 58,6</t>
+          <t>39,41; 57,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,4; 52,99</t>
+          <t>36,94; 52,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,1; 42,98</t>
+          <t>28,63; 43,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,5; 40,38</t>
+          <t>30,95; 40,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,08; 67,3</t>
+          <t>53,11; 68,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,41; 61,21</t>
+          <t>50,03; 61,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,65; 38,72</t>
+          <t>24,32; 38,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,52; 43,53</t>
+          <t>36,72; 43,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,68; 61,77</t>
+          <t>50,72; 62,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,61; 55,75</t>
+          <t>46,28; 56,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,42; 37,93</t>
+          <t>27,67; 38,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,46; 41,05</t>
+          <t>35,35; 41,01</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,29; 14,88</t>
+          <t>12,36; 15,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,63; 16,52</t>
+          <t>13,72; 16,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,43; 11,87</t>
+          <t>9,51; 11,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,78</t>
+          <t>7,38; 10,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,76; 17,67</t>
+          <t>14,82; 17,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,78; 19,64</t>
+          <t>16,83; 19,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,95</t>
+          <t>10,34; 12,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,23</t>
+          <t>9,11; 12,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,04; 16,0</t>
+          <t>13,99; 15,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,69; 17,75</t>
+          <t>15,71; 17,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,11</t>
+          <t>10,31; 12,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,96; 11,33</t>
+          <t>8,98; 11,25</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5848; 19113</t>
+          <t>6385; 20401</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6461; 18538</t>
+          <t>6420; 19166</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7587; 22645</t>
+          <t>7696; 22852</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310; 18929</t>
+          <t>333; 22300</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4194; 15545</t>
+          <t>3637; 14873</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8710; 23966</t>
+          <t>8913; 25116</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5587; 18127</t>
+          <t>5604; 18121</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>238; 15771</t>
+          <t>324; 15030</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11984; 28967</t>
+          <t>12463; 29164</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17185; 36964</t>
+          <t>17201; 37430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15356; 34974</t>
+          <t>15485; 35475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2556; 25817</t>
+          <t>2512; 25955</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12170; 30208</t>
+          <t>11411; 30447</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13830; 31020</t>
+          <t>13428; 30740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13529; 32382</t>
+          <t>13652; 32167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8609; 27837</t>
+          <t>9449; 32563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13572; 31371</t>
+          <t>13806; 30829</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23717; 46154</t>
+          <t>24765; 49101</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10836; 26363</t>
+          <t>10606; 26629</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9167; 29847</t>
+          <t>9101; 31178</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28471; 55013</t>
+          <t>28532; 55370</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42196; 70742</t>
+          <t>42154; 71451</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28257; 52853</t>
+          <t>27814; 52518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21664; 52183</t>
+          <t>22822; 51591</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23898; 45267</t>
+          <t>24259; 47613</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33335; 61390</t>
+          <t>33789; 63243</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14864; 34844</t>
+          <t>14443; 34719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13175; 31285</t>
+          <t>13203; 32527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>37277; 65916</t>
+          <t>38807; 65427</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35084; 64112</t>
+          <t>35520; 62874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28303; 52835</t>
+          <t>28155; 51815</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17528; 32291</t>
+          <t>17425; 32735</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68095; 103129</t>
+          <t>68353; 104063</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76743; 116930</t>
+          <t>75197; 114782</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47522; 77347</t>
+          <t>46401; 78187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34159; 58349</t>
+          <t>33811; 58244</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39745; 67668</t>
+          <t>39029; 68032</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60450; 96874</t>
+          <t>59457; 96031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36857; 65346</t>
+          <t>38408; 66563</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19781; 76651</t>
+          <t>19851; 74954</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43137; 70978</t>
+          <t>43542; 70170</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69702; 106071</t>
+          <t>70086; 105662</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39315; 67337</t>
+          <t>39386; 65850</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36239; 57841</t>
+          <t>36553; 57471</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>88320; 127835</t>
+          <t>89067; 130085</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139902; 191320</t>
+          <t>139374; 190205</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83618; 122052</t>
+          <t>84375; 125373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56490; 121587</t>
+          <t>54239; 124069</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57570; 86017</t>
+          <t>58159; 86675</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79272; 112186</t>
+          <t>78579; 111840</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49495; 79547</t>
+          <t>48663; 81131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50302; 76840</t>
+          <t>50645; 77459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63522; 95052</t>
+          <t>61719; 92589</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77803; 112051</t>
+          <t>77042; 113566</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52246; 83125</t>
+          <t>53235; 85944</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42346; 62564</t>
+          <t>40685; 61730</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129241; 168525</t>
+          <t>128158; 169212</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164418; 216226</t>
+          <t>165536; 215419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112673; 158587</t>
+          <t>111650; 157397</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96703; 130329</t>
+          <t>98167; 129450</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>69371; 97444</t>
+          <t>69011; 97738</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>90652; 123774</t>
+          <t>89806; 124124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44699; 72278</t>
+          <t>44432; 71334</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54702; 79010</t>
+          <t>56153; 80818</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>88272; 118171</t>
+          <t>88898; 118091</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>112107; 146602</t>
+          <t>110058; 144275</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62265; 92667</t>
+          <t>61699; 91712</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36096; 143766</t>
+          <t>38353; 145952</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166469; 205374</t>
+          <t>165331; 205820</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>207947; 257259</t>
+          <t>209453; 259684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114479; 157327</t>
+          <t>115852; 157428</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>79914; 207606</t>
+          <t>80002; 207369</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>53087; 74279</t>
+          <t>49961; 72877</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69157; 97985</t>
+          <t>68313; 96419</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42789; 63207</t>
+          <t>42105; 64137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86780; 111247</t>
+          <t>85279; 111684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>112609; 140123</t>
+          <t>110586; 141888</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>149432; 185092</t>
+          <t>151303; 185457</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56178; 88242</t>
+          <t>55414; 88065</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>149238; 177906</t>
+          <t>150082; 176423</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>169780; 206912</t>
+          <t>169901; 209355</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>227142; 271669</t>
+          <t>225528; 274193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102792; 142209</t>
+          <t>103746; 143103</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>242600; 280881</t>
+          <t>241857; 280615</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>301710; 365333</t>
+          <t>303299; 369199</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>397309; 481554</t>
+          <t>400015; 479745</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>251292; 316354</t>
+          <t>253386; 318699</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>244798; 361711</t>
+          <t>247443; 360860</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>404636; 484194</t>
+          <t>406123; 483010</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>528109; 617858</t>
+          <t>529515; 620549</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>299632; 371248</t>
+          <t>296557; 369711</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>312993; 437865</t>
+          <t>326155; 438160</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>729461; 831117</t>
+          <t>726894; 827500</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>950909; 1076018</t>
+          <t>952121; 1068420</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>571410; 669867</t>
+          <t>570141; 667864</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>620979; 785501</t>
+          <t>622322; 779952</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,68</t>
+          <t>1,72; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,05</t>
+          <t>1,53; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,48</t>
+          <t>1,96; 6,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,82</t>
+          <t>0,32; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,95</t>
+          <t>0,95; 3,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,77</t>
+          <t>2,37; 6,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,15</t>
+          <t>1,53; 5,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,95</t>
+          <t>0,39; 6,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,96</t>
+          <t>1,74; 4,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,99</t>
+          <t>2,32; 5,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,03</t>
+          <t>2,28; 4,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,78</t>
+          <t>0,69; 4,52</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,29</t>
+          <t>2,03; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,15</t>
+          <t>2,28; 5,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,52</t>
+          <t>2,7; 6,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,09</t>
+          <t>2,45; 7,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,63</t>
+          <t>2,41; 5,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,79</t>
+          <t>4,34; 8,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,36</t>
+          <t>2,21; 5,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,24</t>
+          <t>2,46; 6,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,93</t>
+          <t>2,53; 4,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,18</t>
+          <t>3,66; 6,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,31</t>
+          <t>2,67; 5,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,72</t>
+          <t>2,9; 6,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,47</t>
+          <t>4,76; 9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,78</t>
+          <t>5,62; 10,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,22</t>
+          <t>2,8; 6,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,21</t>
+          <t>2,43; 5,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,84</t>
+          <t>6,32; 10,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,53</t>
+          <t>5,58; 9,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,04</t>
+          <t>4,95; 8,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,15</t>
+          <t>3,42; 6,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,4</t>
+          <t>6,22; 9,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,21</t>
+          <t>6,14; 9,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,91</t>
+          <t>4,27; 6,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,52</t>
+          <t>3,35; 5,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 16,81</t>
+          <t>9,76; 16,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 17,69</t>
+          <t>10,74; 17,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,99</t>
+          <t>7,39; 13,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,69</t>
+          <t>5,69; 9,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,91; 15,98</t>
+          <t>9,74; 15,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 18,76</t>
+          <t>12,53; 18,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,09</t>
+          <t>7,22; 12,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,2</t>
+          <t>5,34; 8,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 15,41</t>
+          <t>10,64; 15,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,19</t>
+          <t>12,8; 17,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,86</t>
+          <t>7,95; 11,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,94</t>
+          <t>6,04; 8,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 31,82</t>
+          <t>21,13; 31,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,75; 30,95</t>
+          <t>21,68; 31,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,12; 21,87</t>
+          <t>13,46; 21,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,17</t>
+          <t>9,61; 14,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,02</t>
+          <t>19,55; 28,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,72; 29,07</t>
+          <t>20,2; 28,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 21,71</t>
+          <t>13,72; 21,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,55</t>
+          <t>8,44; 12,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 28,61</t>
+          <t>21,44; 28,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,01; 28,65</t>
+          <t>21,97; 28,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 20,52</t>
+          <t>14,76; 20,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,97</t>
+          <t>9,63; 12,72</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,44; 45,94</t>
+          <t>32,63; 45,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,21; 47,29</t>
+          <t>33,77; 47,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,31; 31,0</t>
+          <t>19,37; 31,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,63; 22,49</t>
+          <t>15,23; 21,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,0; 47,82</t>
+          <t>36,33; 48,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,61; 48,0</t>
+          <t>36,23; 48,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,28; 33,12</t>
+          <t>22,32; 32,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,39; 24,33</t>
+          <t>20,15; 25,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35,96; 44,77</t>
+          <t>35,69; 44,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,2; 46,12</t>
+          <t>37,46; 45,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 31,05</t>
+          <t>22,51; 30,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 21,62</t>
+          <t>18,58; 22,8</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,41; 57,49</t>
+          <t>40,82; 58,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,94; 52,14</t>
+          <t>37,57; 52,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,63; 43,61</t>
+          <t>28,78; 43,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,95; 40,54</t>
+          <t>31,3; 40,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>53,11; 68,15</t>
+          <t>53,24; 67,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,03; 61,33</t>
+          <t>49,28; 61,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,32; 38,65</t>
+          <t>24,45; 38,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,72; 43,17</t>
+          <t>35,72; 42,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,72; 62,5</t>
+          <t>51,04; 61,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,28; 56,26</t>
+          <t>46,81; 56,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,67; 38,17</t>
+          <t>27,68; 38,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,35; 41,01</t>
+          <t>35,02; 40,52</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,04</t>
+          <t>12,22; 15,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,72; 16,46</t>
+          <t>13,75; 16,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,51; 11,96</t>
+          <t>9,57; 11,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,76</t>
+          <t>9,37; 11,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,82; 17,62</t>
+          <t>14,73; 17,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 19,72</t>
+          <t>16,74; 19,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,89</t>
+          <t>10,39; 12,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,24</t>
+          <t>11,31; 13,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,99; 15,93</t>
+          <t>13,91; 15,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,71; 17,63</t>
+          <t>15,67; 17,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 12,07</t>
+          <t>10,38; 12,15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,98; 11,25</t>
+          <t>10,62; 12,01</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9178</t>
+          <t>14493</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6385; 20401</t>
+          <t>6189; 19064</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6420; 19166</t>
+          <t>5817; 18150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7696; 22852</t>
+          <t>6919; 21738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333; 22300</t>
+          <t>1197; 25769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3637; 14873</t>
+          <t>3568; 14823</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8913; 25116</t>
+          <t>8794; 24314</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5604; 18121</t>
+          <t>5398; 18385</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>324; 15030</t>
+          <t>1336; 21173</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12463; 29164</t>
+          <t>12828; 29486</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17201; 37430</t>
+          <t>17440; 37905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15485; 35475</t>
+          <t>16069; 35108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2512; 25955</t>
+          <t>5014; 32653</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35305</t>
+          <t>39503</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11411; 30447</t>
+          <t>11661; 30237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13428; 30740</t>
+          <t>13633; 31914</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13652; 32167</t>
+          <t>13328; 33779</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9449; 32563</t>
+          <t>10908; 34604</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13806; 30829</t>
+          <t>13216; 32419</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24765; 49101</t>
+          <t>24225; 49726</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10606; 26629</t>
+          <t>10982; 26989</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9101; 31178</t>
+          <t>11862; 31674</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28532; 55370</t>
+          <t>28455; 54485</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42154; 71451</t>
+          <t>42320; 69497</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27814; 52518</t>
+          <t>26393; 51632</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22822; 51591</t>
+          <t>26933; 56634</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45052</t>
+          <t>51307</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24259; 47613</t>
+          <t>23959; 47494</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33789; 63243</t>
+          <t>32947; 60054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14443; 34719</t>
+          <t>15596; 37065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13203; 32527</t>
+          <t>14620; 34244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38807; 65427</t>
+          <t>38131; 65215</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35520; 62874</t>
+          <t>36811; 64917</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28155; 51815</t>
+          <t>28365; 51126</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17425; 32735</t>
+          <t>20781; 38579</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68353; 104063</t>
+          <t>68816; 106330</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75197; 114782</t>
+          <t>76456; 117875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46401; 78187</t>
+          <t>48321; 76554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33811; 58244</t>
+          <t>40485; 66787</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>51598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>46290</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>101561</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39029; 68032</t>
+          <t>39519; 68394</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59457; 96031</t>
+          <t>58286; 95848</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38408; 66563</t>
+          <t>37847; 66877</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19851; 74954</t>
+          <t>38593; 66814</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43542; 70170</t>
+          <t>42798; 69730</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70086; 105662</t>
+          <t>70569; 104931</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39386; 65850</t>
+          <t>39358; 68115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36553; 57471</t>
+          <t>38509; 60469</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89067; 130085</t>
+          <t>89837; 131186</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139374; 190205</t>
+          <t>141643; 192974</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84375; 125373</t>
+          <t>84020; 122522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54239; 124069</t>
+          <t>84588; 119952</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62990</t>
+          <t>70291</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50949</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>130725</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58159; 86675</t>
+          <t>57554; 85894</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78579; 111840</t>
+          <t>78318; 113097</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48663; 81131</t>
+          <t>49935; 79970</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50645; 77459</t>
+          <t>57039; 85991</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61719; 92589</t>
+          <t>62369; 91855</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77042; 113566</t>
+          <t>78920; 112632</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>53235; 85944</t>
+          <t>54297; 86866</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40685; 61730</t>
+          <t>50303; 71935</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128158; 169212</t>
+          <t>126773; 170269</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165536; 215419</t>
+          <t>165210; 215812</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>111650; 157397</t>
+          <t>113214; 156664</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98167; 129450</t>
+          <t>114569; 151215</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66793</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>91482</t>
+          <t>98578</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>158275</t>
+          <t>170420</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>69011; 97738</t>
+          <t>69434; 95951</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>89806; 124124</t>
+          <t>88650; 123890</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44432; 71334</t>
+          <t>44571; 73199</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56153; 80818</t>
+          <t>60588; 85391</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>88898; 118091</t>
+          <t>89716; 119256</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>110058; 144275</t>
+          <t>108911; 144677</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61699; 91712</t>
+          <t>61804; 90545</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>38353; 145952</t>
+          <t>86416; 111185</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>165331; 205820</t>
+          <t>164082; 204870</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>209453; 259684</t>
+          <t>210902; 257995</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>115852; 157428</t>
+          <t>114135; 156487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>80002; 207369</t>
+          <t>153599; 188495</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98685</t>
+          <t>107484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>162727</t>
+          <t>174377</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>261412</t>
+          <t>281861</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>49961; 72877</t>
+          <t>51749; 74526</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68313; 96419</t>
+          <t>69478; 96702</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42105; 64137</t>
+          <t>42320; 64099</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85279; 111684</t>
+          <t>94642; 121052</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>110586; 141888</t>
+          <t>110854; 140549</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>151303; 185457</t>
+          <t>149022; 184996</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55414; 88065</t>
+          <t>55714; 88021</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>150082; 176423</t>
+          <t>159226; 190020</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>169901; 209355</t>
+          <t>170966; 207021</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>225528; 274193</t>
+          <t>228132; 274306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103746; 143103</t>
+          <t>103772; 143759</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>241857; 280615</t>
+          <t>261984; 303160</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>320615</t>
+          <t>352339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>437533</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>718545</t>
+          <t>789872</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>303299; 369199</t>
+          <t>299928; 369344</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>400015; 479745</t>
+          <t>400853; 482157</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>253386; 318699</t>
+          <t>254844; 317446</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>247443; 360860</t>
+          <t>318270; 390567</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>406123; 483010</t>
+          <t>403825; 477766</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>529515; 620549</t>
+          <t>526808; 614330</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>296557; 369711</t>
+          <t>298011; 372425</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>326155; 438160</t>
+          <t>410127; 473377</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>726894; 827500</t>
+          <t>722756; 825630</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>952121; 1068420</t>
+          <t>949783; 1070834</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>570141; 667864</t>
+          <t>574241; 672027</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>622322; 779952</t>
+          <t>746058; 843528</t>
         </is>
       </c>
     </row>
